--- a/src/main/resources/espacios/Politica/0 - Politica.xlsx
+++ b/src/main/resources/espacios/Politica/0 - Politica.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="138">
   <si>
     <t xml:space="preserve">Political Ideologies</t>
   </si>
@@ -187,7 +187,7 @@
     <t xml:space="preserve">They prioritize economic freedom, private property</t>
   </si>
   <si>
-    <t xml:space="preserve">Dan prioridad a la libertad económica, la propiedad privada y la preservación del orden social tradicional.</t>
+    <t xml:space="preserve">Dan prioridad a la libertad económica, la propiedad privada</t>
   </si>
   <si>
     <t xml:space="preserve">ðeɪ praɪˈɔrəˌtaɪz ˌɛkəˈnɑmɪk ˈfridəm, ˈpraɪvət ˈprɑpərti</t>
@@ -196,238 +196,241 @@
     <t xml:space="preserve">and the preservation of traditional social order.</t>
   </si>
   <si>
+    <t xml:space="preserve">y la preservación del orden social tradicional.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ænd ðə ˌprɛzərˈveɪʃən ʌv trəˈdɪʃənəl ˈsoʊʃəl ˈɔrdər.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classical Liberalism:</t>
+  </si>
+  <si>
     <t xml:space="preserve">Liberalismo Clásico:</t>
   </si>
   <si>
-    <t xml:space="preserve">ænd ðə ˌprɛzərˈveɪʃən ʌv trəˈdɪʃənəl ˈsoʊʃəl ˈɔrdər.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classical Liberalism:</t>
+    <t xml:space="preserve">ˈklæsɪkəl ˈlɪbərəˌlɪzəm:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supports free markets, individual rights, and limited government (e.g., Adam Smith, John Locke).</t>
   </si>
   <si>
     <t xml:space="preserve">Apoya los mercados libres, los derechos individuales y un gobierno limitado (ej., Adam Smith, John Locke).</t>
   </si>
   <si>
-    <t xml:space="preserve">ˈklæsɪkəl ˈlɪbərəˌlɪzəm:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supports free markets, individual rights, and limited government (e.g., Adam Smith, John Locke).</t>
+    <t xml:space="preserve">səˈpɔrts fri ˈmɑrkəts, ˌɪndəˈvɪʤəwəl raɪts, ænd ˈlɪmɪtɪd ˈɡʌvərmənt (i.ʤi., ˈædəm smɪθ, ʤɑn lɑk).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conservatism:</t>
   </si>
   <si>
     <t xml:space="preserve">Conservadurismo:</t>
   </si>
   <si>
-    <t xml:space="preserve">səˈpɔrts fri ˈmɑrkəts, ˌɪndəˈvɪʤəwəl raɪts, ænd ˈlɪmɪtɪd ˈɡʌvərmənt (i.ʤi., ˈædəm smɪθ, ʤɑn lɑk).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conservatism:</t>
+    <t xml:space="preserve">kənˈsɜrvəˌtɪzəm:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aims to preserve traditions, religious values, and social stability with minimal state intervention in the economy.</t>
   </si>
   <si>
     <t xml:space="preserve">Busca preservar las tradiciones, los valores religiosos y la estabilidad social, con mínima intervención estatal en la economía.</t>
   </si>
   <si>
-    <t xml:space="preserve">kənˈsɜrvəˌtɪzəm:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aims to preserve traditions, religious values, and social stability with minimal state intervention in the economy.</t>
+    <t xml:space="preserve">eɪmz tu prəˈzɜrv trəˈdɪʃənz, rɪˈlɪʤəs ˈvæljuz, ænd ˈsoʊʃəl stəˈbɪlɪti wɪð ˈmɪnəməl steɪt ˌɪntərˈvɛnʧən ɪn ði ɪˈkɑnəmi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nationalism:</t>
   </si>
   <si>
     <t xml:space="preserve">Nacionalismo:</t>
   </si>
   <si>
-    <t xml:space="preserve">eɪmz tu prəˈzɜrv trəˈdɪʃənz, rɪˈlɪʤəs ˈvæljuz, ænd ˈsoʊʃəl stəˈbɪlɪti wɪð ˈmɪnəməl steɪt ˌɪntərˈvɛnʧən ɪn ði ɪˈkɑnəmi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nationalism:</t>
+    <t xml:space="preserve">ˈnæʃənəˌlɪzəm:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emphasizes national identity and sovereignty, sometimes with protectionist or xenophobic policies.</t>
   </si>
   <si>
     <t xml:space="preserve">Enfatiza la identidad y la soberanía nacional, a veces con políticas proteccionistas o xenófobas.</t>
   </si>
   <si>
-    <t xml:space="preserve">ˈnæʃənəˌlɪzəm:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emphasizes national identity and sovereignty, sometimes with protectionist or xenophobic policies.</t>
+    <t xml:space="preserve">ˈɛmfəˌsaɪzəz ˈnæʃənəl aɪˈdɛntəti ænd ˈsɑvrənti, səmˈtaɪmz wɪð prəˈtɛkʃənɪst ɔr ˌzɛnəˈfɑbɪk ˈpɑləsiz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neoliberalism:</t>
   </si>
   <si>
     <t xml:space="preserve">Neoliberalismo:</t>
   </si>
   <si>
-    <t xml:space="preserve">ˈɛmfəˌsaɪzəz ˈnæʃənəl aɪˈdɛntəti ænd ˈsɑvrənti, səmˈtaɪmz wɪð prəˈtɛkʃənɪst ɔr ˌzɛnəˈfɑbɪk ˈpɑləsiz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neoliberalism:</t>
+    <t xml:space="preserve">ˌnioʊˈlɪbərəlɪzᵊm:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promotes free markets, privatization of public enterprises, and reducing the state's role in the economy.</t>
   </si>
   <si>
     <t xml:space="preserve">Promueve los mercados libres, la privatización de empresas públicas y la reducción del papel del Estado en la economía.</t>
   </si>
   <si>
-    <t xml:space="preserve">ˌnioʊˈlɪbərəlɪzᵊm:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promotes free markets, privatization of public enterprises, and reducing the state's role in the economy.</t>
+    <t xml:space="preserve">prəˈmoʊts fri ˈmɑrkəts, ˈpraɪvətəˈzeɪʃən ʌv ˈpʌblɪk ˈɛntərˌpraɪzɪz, ænd rəˈdusɪŋ ðə steɪts roʊl ɪn ði ɪˈkɑnəmi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Authoritarian Ideologies:</t>
   </si>
   <si>
     <t xml:space="preserve">Ideologías Autoritarias</t>
   </si>
   <si>
-    <t xml:space="preserve">prəˈmoʊts fri ˈmɑrkəts, ˈpraɪvətəˈzeɪʃən ʌv ˈpʌblɪk ˈɛntərˌpraɪzɪz, ænd rəˈdusɪŋ ðə steɪts roʊl ɪn ði ɪˈkɑnəmi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Authoritarian Ideologies:</t>
+    <t xml:space="preserve">əˌθɔrəˈtɛriən ˌaɪdiˈɑləʤiz:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They favor a strong state with centralized control and limitations on individual freedoms.</t>
   </si>
   <si>
     <t xml:space="preserve">Favorecen un Estado fuerte con control centralizado y limitaciones a las libertades individuales.</t>
   </si>
   <si>
-    <t xml:space="preserve">əˌθɔrəˈtɛriən ˌaɪdiˈɑləʤiz:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">They favor a strong state with centralized control and limitations on individual freedoms.</t>
+    <t xml:space="preserve">ðeɪ ˈfeɪvər ə strɔŋ steɪt wɪð ˈsɛntrəˌlaɪzd kənˈtroʊl ænd ˌlɪmɪˈteɪʃənz ɑn ˌɪndəˈvɪʤəwəl ˈfridəmz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fascism:</t>
   </si>
   <si>
     <t xml:space="preserve">Fascismo:</t>
   </si>
   <si>
-    <t xml:space="preserve">ðeɪ ˈfeɪvər ə strɔŋ steɪt wɪð ˈsɛntrəˌlaɪzd kənˈtroʊl ænd ˌlɪmɪˈteɪʃənz ɑn ˌɪndəˈvɪʤəwəl ˈfridəmz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fascism:</t>
+    <t xml:space="preserve">ˈfæˌʃɪzəm:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme nationalism, militarism, state control, and suppression of opposition (e.g., Mussolini, Hitler).</t>
   </si>
   <si>
     <t xml:space="preserve">Nacionalismo extremo, militarismo, control estatal y supresión de la oposición (ej., Mussolini, Hitler).</t>
   </si>
   <si>
-    <t xml:space="preserve">ˈfæˌʃɪzəm:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme nationalism, militarism, state control, and suppression of opposition (e.g., Mussolini, Hitler).</t>
+    <t xml:space="preserve">ɛkˈstrim ˈnæʃənəˌlɪzəm, ˈmɪlətəˌrɪzəm, steɪt kənˈtroʊl, ænd səˈprɛʃən ʌv ˌɑpəˈzɪʃən (i.ʤi., ˌmusoʊˈlini, ˈhɪtlər).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totalitarianism:</t>
   </si>
   <si>
     <t xml:space="preserve">Totalitarismo:</t>
   </si>
   <si>
-    <t xml:space="preserve">ɛkˈstrim ˈnæʃənəˌlɪzəm, ˈmɪlətəˌrɪzəm, steɪt kənˈtroʊl, ænd səˈprɛʃən ʌv ˌɑpəˈzɪʃən (i.ʤi., ˌmusoʊˈlini, ˈhɪtlər).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Totalitarianism:</t>
+    <t xml:space="preserve">ˌtoʊˌtæləˈtɛriəˌnɪzəm:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Absolute state control over all aspects of social, economic, and political life (e.g., Stalin in the USSR, Mao in China).</t>
   </si>
   <si>
     <t xml:space="preserve">Control absoluto del Estado sobre todos los aspectos de la vida social, económica y política (ej., Stalin en la URSS, Mao en China).</t>
   </si>
   <si>
-    <t xml:space="preserve">ˌtoʊˌtæləˈtɛriəˌnɪzəm:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Absolute state control over all aspects of social, economic, and political life (e.g., Stalin in the USSR, Mao in China).</t>
+    <t xml:space="preserve">ˈæbsəˌlut steɪt kənˈtroʊl ˈoʊvər ɔl ˈæˌspɛkts ʌv ˈsoʊʃəl, ˌɛkəˈnɑmɪk, ænd pəˈlɪtəkəl laɪf (i.ʤi., ˈstɑlən ɪn ðə ju-ɛs-ɛs-ɑr, maʊ ɪn ˈʧaɪnə).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Populism:</t>
   </si>
   <si>
     <t xml:space="preserve">Populismo:</t>
   </si>
   <si>
-    <t xml:space="preserve">ˈæbsəˌlut steɪt kənˈtroʊl ˈoʊvər ɔl ˈæˌspɛkts ʌv ˈsoʊʃəl, ˌɛkəˈnɑmɪk, ænd pəˈlɪtəkəl laɪf (i.ʤi., ˈstɑlən ɪn ðə ju-ɛs-ɛs-ɑr, maʊ ɪn ˈʧaɪnə).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Populism:</t>
+    <t xml:space="preserve">ˈpɑpjəˌlɪzəm:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not an ideology itself</t>
   </si>
   <si>
     <t xml:space="preserve">No es una ideología en sí,</t>
   </si>
   <si>
-    <t xml:space="preserve">ˈpɑpjəˌlɪzəm:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not an ideology itself</t>
+    <t xml:space="preserve">nɑt ən ˌaɪdiˈɑləʤi ɪtˈsɛlf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">but a political approach that frames politics as a struggle between "the people"</t>
   </si>
   <si>
     <t xml:space="preserve">sino un enfoque político que presenta la política como una lucha entre "el pueblo"</t>
   </si>
   <si>
-    <t xml:space="preserve">nɑt ən ˌaɪdiˈɑləʤi ɪtˈsɛlf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">but a political approach that frames politics as a struggle between "the people"</t>
+    <t xml:space="preserve">bʌt ə pəˈlɪtəkəl əˈproʊʧ ðæt freɪmz ˈpɑləˌtɪks æz ə ˈstrʌɡəl bɪˈtwin "ðə ˈpipəl"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">and "the elites," often justifying strong leadership.</t>
   </si>
   <si>
     <t xml:space="preserve">y "las élites", a menudo justificando un liderazgo fuerte.</t>
   </si>
   <si>
-    <t xml:space="preserve">bʌt ə pəˈlɪtəkəl əˈproʊʧ ðæt freɪmz ˈpɑləˌtɪks æz ə ˈstrʌɡəl bɪˈtwin "ðə ˈpipəl"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">and "the elites," often justifying strong leadership.</t>
+    <t xml:space="preserve">ænd "ði ɪˈlits," ˈɔfən ˈʤʌstəˌfaɪɪŋ strɔŋ ˈlidərˌʃɪp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centrist and Mixed Ideologies</t>
   </si>
   <si>
     <t xml:space="preserve">Ideologías Centristas y Mixtas</t>
   </si>
   <si>
-    <t xml:space="preserve">ænd "ði ɪˈlits," ˈɔfən ˈʤʌstəˌfaɪɪŋ strɔŋ ˈlidərˌʃɪp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centrist and Mixed Ideologies</t>
+    <t xml:space="preserve">ˈsɛntrɪst ænd mɪkst ˌaɪdiˈɑləʤiz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They seek a balance between state intervention and individual freedom.</t>
   </si>
   <si>
     <t xml:space="preserve">Buscan un equilibrio entre la intervención del Estado y la libertad individual.</t>
   </si>
   <si>
-    <t xml:space="preserve">ˈsɛntrɪst ænd mɪkst ˌaɪdiˈɑləʤiz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">They seek a balance between state intervention and individual freedom.</t>
+    <t xml:space="preserve">ðeɪ sik ə ˈbæləns bɪˈtwin steɪt ˌɪntərˈvɛnʧən ænd ˌɪndəˈvɪʤəwəl ˈfridəm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Social Democracy:</t>
   </si>
   <si>
     <t xml:space="preserve">Socialdemocracia:</t>
   </si>
   <si>
-    <t xml:space="preserve">ðeɪ sik ə ˈbæləns bɪˈtwin steɪt ˌɪntərˈvɛnʧən ænd ˌɪndəˈvɪʤəwəl ˈfridəm.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Social Democracy:</t>
+    <t xml:space="preserve">ˈsoʊʃəl dɪˈmɑkrəsi:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accepts a market economy but implements social policies to reduce inequalities (e.g., Nordic countries).</t>
   </si>
   <si>
     <t xml:space="preserve">Acepta la economía de mercado pero implementa políticas sociales para reducir las desigualdades (ej., países nórdicos).</t>
   </si>
   <si>
-    <t xml:space="preserve">ˈsoʊʃəl dɪˈmɑkrəsi:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accepts a market economy but implements social policies to reduce inequalities (e.g., Nordic countries).</t>
+    <t xml:space="preserve">ækˈsɛpts ə ˈmɑrkət ɪˈkɑnəmi bʌt ˈɪmpləmənts ˈsoʊʃəl ˈpɑləsiz tu rəˈdus ˌɪnəˈkwɑlɪtiz (i.ʤi., ˈnɔrdɪk ˈkʌntriz).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christian Democracy:</t>
   </si>
   <si>
     <t xml:space="preserve">Democracia Cristiana:</t>
   </si>
   <si>
-    <t xml:space="preserve">ækˈsɛpts ə ˈmɑrkət ɪˈkɑnəmi bʌt ˈɪmpləmənts ˈsoʊʃəl ˈpɑləsiz tu rəˈdus ˌɪnəˈkwɑlɪtiz (i.ʤi., ˈnɔrdɪk ˈkʌntriz).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christian Democracy:</t>
+    <t xml:space="preserve">ˈkrɪsʧən dɪˈmɑkrəsi:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combines religious values with welfare policies and a market economy.</t>
   </si>
   <si>
     <t xml:space="preserve">Combina valores religiosos con políticas de bienestar y una economía de mercado.</t>
   </si>
   <si>
-    <t xml:space="preserve">ˈkrɪsʧən dɪˈmɑkrəsi:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combines religious values with welfare policies and a market economy.</t>
+    <t xml:space="preserve">kəmˈbaɪnz rɪˈlɪʤəs ˈvæljuz wɪð ˈwɛlˌfɛr ˈpɑləsiz ænd ə ˈmɑrkət ɪˈkɑnəmi.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Social Liberalism:</t>
   </si>
   <si>
     <t xml:space="preserve">Liberalismo Social:</t>
   </si>
   <si>
-    <t xml:space="preserve">kəmˈbaɪnz rɪˈlɪʤəs ˈvæljuz wɪð ˈwɛlˌfɛr ˈpɑləsiz ænd ə ˈmɑrkət ɪˈkɑnəmi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Social Liberalism:</t>
+    <t xml:space="preserve">ˈsoʊʃəl ˈlɪbərəˌlɪzəm:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supports a market economy with regulations to ensure rights and social welfare.</t>
   </si>
   <si>
     <t xml:space="preserve">Apoya una economía de mercado con regulaciones para garantizar los derechos y el bienestar social.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈsoʊʃəl ˈlɪbərəˌlɪzəm:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supports a market economy with regulations to ensure rights and social welfare.</t>
   </si>
   <si>
     <t xml:space="preserve">səˈpɔrts ə ˈmɑrkət ɪˈkɑnəmi wɪð ˌrɛɡjəˈleɪʃənz tu ɛnˈʃʊr raɪts ænd ˈsoʊʃəl ˈwɛlˌfɛr.</t>
@@ -440,7 +443,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -461,6 +464,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -511,12 +519,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -644,7 +656,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F46"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="126.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="135.51"/>
@@ -920,7 +932,7 @@
       <c r="A20" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>58</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -1281,8 +1293,11 @@
       <c r="A46" s="1" t="s">
         <v>135</v>
       </c>
+      <c r="B46" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="D46" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>6</v>

--- a/src/main/resources/espacios/Politica/0 - Politica.xlsx
+++ b/src/main/resources/espacios/Politica/0 - Politica.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="138">
   <si>
     <t xml:space="preserve">Political Ideologies</t>
   </si>
@@ -443,7 +443,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -464,11 +464,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -528,7 +523,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -952,6 +947,9 @@
       <c r="D21" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="F21" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
